--- a/Model/PL.xlsx
+++ b/Model/PL.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhv\OneDrive\Documents\GitHub\modelz\Model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\minhv\OneDrive\Documents\GitHub\models\modelz\Model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57B0C392-BA2E-4412-B162-0E1AA81C2005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A49EFC-FD5E-4443-A283-14ADE7A53017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28800" yWindow="0" windowWidth="28800" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Assumptions" sheetId="1" r:id="rId1"/>
+    <sheet name="DCF" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
     <author>Minh Nguyen Viet Quang</author>
   </authors>
   <commentList>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{B8DF0D60-ED6B-4F83-8D51-57D82ED49C42}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{B8DF0D60-ED6B-4F83-8D51-57D82ED49C42}">
       <text>
         <r>
           <rPr>
@@ -66,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{8E703E69-2F3B-455F-9865-D7BD6206FE4B}">
+    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{8E703E69-2F3B-455F-9865-D7BD6206FE4B}">
       <text>
         <r>
           <rPr>
@@ -79,7 +81,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{63179CB5-82F3-4FBB-A262-505F5DA71628}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{63179CB5-82F3-4FBB-A262-505F5DA71628}">
       <text>
         <r>
           <rPr>
@@ -92,7 +94,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0" shapeId="0" xr:uid="{EA05724F-CD5C-4D80-A9C7-0333D1734687}">
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{EA05724F-CD5C-4D80-A9C7-0333D1734687}">
       <text>
         <r>
           <rPr>
@@ -105,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{6DBC38F2-1323-46C0-BEC4-F78FE805B8FF}">
+    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{6DBC38F2-1323-46C0-BEC4-F78FE805B8FF}">
       <text>
         <r>
           <rPr>
@@ -146,7 +148,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="123">
   <si>
     <t>x</t>
   </si>
@@ -371,17 +373,203 @@
   </si>
   <si>
     <t>(numbers all in thousands unless stated otherwise, $US, all figures EoP except a few in CF statement)</t>
+  </si>
+  <si>
+    <t>Comparables</t>
+  </si>
+  <si>
+    <t>Public</t>
+  </si>
+  <si>
+    <t>Private</t>
+  </si>
+  <si>
+    <t>Patent Expiry:</t>
+  </si>
+  <si>
+    <t>&gt; 25 Years:</t>
+  </si>
+  <si>
+    <t>Whole Earth Imaging</t>
+  </si>
+  <si>
+    <t>ICEYE</t>
+  </si>
+  <si>
+    <t>Capella Space</t>
+  </si>
+  <si>
+    <t>Spire Global</t>
+  </si>
+  <si>
+    <t>Airbus Defence</t>
+  </si>
+  <si>
+    <t>BlackSky</t>
+  </si>
+  <si>
+    <t>Vantor</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Current Price</t>
+  </si>
+  <si>
+    <t>Price Ratio</t>
+  </si>
+  <si>
+    <t>P/E</t>
+  </si>
+  <si>
+    <t>P/B</t>
+  </si>
+  <si>
+    <t>Capital Structure</t>
+  </si>
+  <si>
+    <t>% Debt</t>
+  </si>
+  <si>
+    <t>% LT Debt</t>
+  </si>
+  <si>
+    <t>% ST Debt</t>
+  </si>
+  <si>
+    <t>Liquidity Ratio</t>
+  </si>
+  <si>
+    <r>
+      <t>Cash / CAOPEX</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Capital Expediture + Operating Expense</t>
+    </r>
+  </si>
+  <si>
+    <t>Cash / Interest Expense</t>
+  </si>
+  <si>
+    <t>Free Cash Flow</t>
+  </si>
+  <si>
+    <t>TTM FCFF Yield %</t>
+  </si>
+  <si>
+    <t>YOY Growth (%)</t>
+  </si>
+  <si>
+    <t>FCFF</t>
+  </si>
+  <si>
+    <t>Operating Expense</t>
+  </si>
+  <si>
+    <t>&lt; does PL have a patent for this?</t>
+  </si>
+  <si>
+    <t>Satellogic</t>
+  </si>
+  <si>
+    <t>ImageSat</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">CG Satellite </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(I believe this is CN ChangGuang)</t>
+    </r>
+  </si>
+  <si>
+    <t>FY 2023</t>
+  </si>
+  <si>
+    <t>FY 24</t>
+  </si>
+  <si>
+    <t>FY 25</t>
+  </si>
+  <si>
+    <t>FY 26</t>
+  </si>
+  <si>
+    <t>FY27</t>
+  </si>
+  <si>
+    <t>FY28</t>
+  </si>
+  <si>
+    <t>Net Loss</t>
+  </si>
+  <si>
+    <t>- CAPEX</t>
+  </si>
+  <si>
+    <t>- Change in NWC</t>
+  </si>
+  <si>
+    <t>+ D&amp;A</t>
+  </si>
+  <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>Market Capitalization</t>
+  </si>
+  <si>
+    <t>Net Cash</t>
+  </si>
+  <si>
+    <t>Total Liabilitty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="&quot;FY&quot;General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -486,6 +674,41 @@
       <color rgb="FFC00000"/>
       <name val="Airal"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u val="singleAccounting"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u val="singleAccounting"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -501,7 +724,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -598,12 +821,83 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -630,7 +924,7 @@
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -644,9 +938,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -662,6 +956,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -949,7 +1276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Z62"/>
   <sheetFormatPr defaultRowHeight="12.75" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="32" customWidth="1"/>
@@ -1237,534 +1564,837 @@
       <c r="Y9" s="26"/>
       <c r="Z9" s="27"/>
     </row>
-    <row r="10" spans="1:26">
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="2" t="s">
+    <row r="11" spans="1:26">
+      <c r="B11" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="B12" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="B13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
-      <c r="B11" s="2" t="s">
+    <row r="24" spans="1:26">
+      <c r="B24" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E24" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K24" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="S24" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
-      <c r="B12" s="4" t="s">
+    <row r="25" spans="1:26">
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="39">
+      <c r="C25" s="39">
         <v>442</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D25" s="2">
         <v>618</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E25" s="2">
         <v>770</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T25" s="2">
         <v>2015</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
-      <c r="B13" s="4" t="s">
+    <row r="26" spans="1:26">
+      <c r="B26" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="4"/>
-      <c r="D13" s="2" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="S26" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T26" s="2">
         <v>2017</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="E14" s="2" t="s">
+    <row r="27" spans="1:26" s="5" customFormat="1">
+      <c r="A27" s="33"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T27" s="2">
         <v>2019</v>
       </c>
-    </row>
-    <row r="15" spans="1:26">
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="E15" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26">
-      <c r="B16" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16">
-        <v>1.02</v>
-      </c>
-      <c r="E16" s="16">
-        <v>1.1299999999999999</v>
-      </c>
-      <c r="F16" s="16">
-        <v>1.08</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16">
-      <c r="B17" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="16">
-        <v>1.03</v>
-      </c>
-      <c r="E17" s="16">
-        <v>1.17</v>
-      </c>
-      <c r="F17" s="16">
-        <v>1.1599999999999999</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16">
-      <c r="B18" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="2">
-        <v>442</v>
-      </c>
-      <c r="E18" s="2">
-        <v>618</v>
-      </c>
-      <c r="F18" s="2">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16">
-      <c r="B19" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="16">
-        <v>0.88</v>
-      </c>
-      <c r="E19" s="16">
-        <v>0.92</v>
-      </c>
-      <c r="F19" s="16">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16">
-      <c r="B20" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="8">
-        <f>+D23/D12</f>
-        <v>154.91262135922329</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-    </row>
-    <row r="21" spans="1:16">
-      <c r="B21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-    </row>
-    <row r="22" spans="1:16">
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-    </row>
-    <row r="23" spans="1:16" s="5" customFormat="1">
-      <c r="A23" s="33"/>
-      <c r="B23" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="17">
-        <f>+D36</f>
-        <v>95736</v>
-      </c>
-      <c r="K23" s="5" cm="1">
-        <f t="array" ref="K23">+_xlfn.IFNA(SUM(G23:J23),blank)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16">
-      <c r="K24" s="2" cm="1">
-        <f t="array" ref="K24">+_xlfn.IFNA(SUM(G24:J24),blank)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16">
-      <c r="B25" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="2" cm="1">
-        <f t="array" ref="K25">+_xlfn.IFNA(SUM(G25:J25),blank)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16">
-      <c r="B26" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C26" s="4"/>
-      <c r="K26" s="2" cm="1">
-        <f t="array" ref="K26">+_xlfn.IFNA(SUM(G26:J26),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P26" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16">
-      <c r="B27" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="K27" s="2" cm="1">
-        <f t="array" ref="K27">+_xlfn.IFNA(SUM(G27:J27),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P27" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16">
-      <c r="B28" s="4" t="s">
-        <v>4</v>
-      </c>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="E28" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="K28" s="2" cm="1">
-        <f t="array" ref="K28">+_xlfn.IFNA(SUM(G28:J28),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P28" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16">
-      <c r="B29" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="4"/>
-      <c r="K29" s="2" cm="1">
-        <f t="array" ref="K29">+_xlfn.IFNA(SUM(G29:J29),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P29" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16">
-      <c r="H30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="K30" s="2" cm="1">
-        <f t="array" ref="K30">+_xlfn.IFNA(SUM(G30:J30),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16">
-      <c r="B31" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K31" s="2" cm="1">
-        <f t="array" ref="K31">+_xlfn.IFNA(SUM(G31:J31),blank)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16">
-      <c r="B32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="K32" s="2" cm="1">
-        <f t="array" ref="K32">+_xlfn.IFNA(SUM(G32:J32),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P32" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16">
-      <c r="B33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="E33" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="K33" s="2" cm="1">
-        <f t="array" ref="K33">+_xlfn.IFNA(SUM(G33:J33),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P33" s="2" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16">
-      <c r="B34" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C34" s="4"/>
-      <c r="E34" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K34" s="2" cm="1">
-        <f t="array" ref="K34">+_xlfn.IFNA(SUM(G34:J34),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P34" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16">
-      <c r="E35" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K35" s="2" cm="1">
-        <f t="array" ref="K35">+_xlfn.IFNA(SUM(G35:J35),blank)</f>
-        <v>0</v>
-      </c>
-      <c r="P35" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16">
-      <c r="B36" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D36" s="8">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
+      <c r="B29" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16">
+        <v>1.02</v>
+      </c>
+      <c r="E29" s="16">
+        <v>1.1299999999999999</v>
+      </c>
+      <c r="F29" s="16">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
+      <c r="B30" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="16">
+        <v>1.03</v>
+      </c>
+      <c r="E30" s="16">
+        <v>1.17</v>
+      </c>
+      <c r="F30" s="16">
+        <v>1.1599999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="B31" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="15"/>
+      <c r="D31" s="2">
+        <v>442</v>
+      </c>
+      <c r="E31" s="2">
+        <v>618</v>
+      </c>
+      <c r="F31" s="2">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26">
+      <c r="B32" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="15"/>
+      <c r="D32" s="16">
+        <v>0.88</v>
+      </c>
+      <c r="E32" s="16">
+        <v>0.92</v>
+      </c>
+      <c r="F32" s="16">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26">
+      <c r="B33" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="15"/>
+      <c r="D33" s="8">
+        <f>+D36/D25</f>
+        <v>154.91262135922329</v>
+      </c>
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+    </row>
+    <row r="34" spans="1:26">
+      <c r="B34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+    </row>
+    <row r="35" spans="1:26">
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+    </row>
+    <row r="36" spans="1:26">
+      <c r="B36" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="5"/>
+      <c r="D36" s="17">
+        <f>+D49</f>
         <v>95736</v>
       </c>
-      <c r="K36" s="2" cm="1">
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5" cm="1">
         <f t="array" ref="K36">+_xlfn.IFNA(SUM(G36:J36),blank)</f>
         <v>0</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" s="13" customFormat="1">
-      <c r="A37" s="34"/>
-      <c r="B37" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="14">
-        <v>102393</v>
-      </c>
-      <c r="K37" s="13" cm="1">
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+      <c r="S36" s="5"/>
+      <c r="T36" s="5"/>
+      <c r="U36" s="5"/>
+      <c r="V36" s="5"/>
+      <c r="W36" s="5"/>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+    </row>
+    <row r="37" spans="1:26">
+      <c r="K37" s="2" cm="1">
         <f t="array" ref="K37">+_xlfn.IFNA(SUM(G37:J37),blank)</f>
         <v>0</v>
       </c>
-      <c r="P37" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" s="5" customFormat="1">
-      <c r="A38" s="33"/>
-      <c r="B38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" s="9">
-        <f>+D36-D37</f>
-        <v>-6657</v>
-      </c>
-      <c r="K38" s="5" cm="1">
+    </row>
+    <row r="38" spans="1:26">
+      <c r="B38" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2" cm="1">
         <f t="array" ref="K38">+_xlfn.IFNA(SUM(G38:J38),blank)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
-      <c r="B39" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39" s="8">
-        <v>37871</v>
-      </c>
+    <row r="39" spans="1:26">
+      <c r="B39" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="4"/>
       <c r="K39" s="2" cm="1">
         <f t="array" ref="K39">+_xlfn.IFNA(SUM(G39:J39),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:16">
-      <c r="B40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="8">
-        <v>34913</v>
-      </c>
+      <c r="P39" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26">
+      <c r="B40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4"/>
       <c r="K40" s="2" cm="1">
         <f t="array" ref="K40">+_xlfn.IFNA(SUM(G40:J40),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" s="11" customFormat="1" ht="15">
-      <c r="A41" s="35"/>
-      <c r="B41" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="10">
-        <v>27019</v>
-      </c>
-      <c r="K41" s="5" cm="1">
+      <c r="P40" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" s="13" customFormat="1">
+      <c r="A41" s="34"/>
+      <c r="B41" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2" cm="1">
         <f t="array" ref="K41">+_xlfn.IFNA(SUM(G41:J41),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" s="12" customFormat="1" ht="15">
-      <c r="A42" s="36"/>
-      <c r="B42" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="10">
-        <f>+SUM(D39:D41)</f>
-        <v>99803</v>
-      </c>
-      <c r="K42" s="12" cm="1">
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+    </row>
+    <row r="42" spans="1:26" s="5" customFormat="1">
+      <c r="A42" s="33"/>
+      <c r="B42" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2" cm="1">
         <f t="array" ref="K42">+_xlfn.IFNA(SUM(G42:J42),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" s="5" customFormat="1">
-      <c r="A43" s="33"/>
-      <c r="B43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D43" s="9">
-        <f>+D38-D42</f>
-        <v>-106460</v>
-      </c>
-      <c r="K43" s="5" cm="1">
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+    </row>
+    <row r="43" spans="1:26">
+      <c r="H43" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K43" s="2" cm="1">
         <f t="array" ref="K43">+_xlfn.IFNA(SUM(G43:J43),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="1:16">
+      <c r="P43" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="44" spans="1:26">
       <c r="B44" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="8">
-        <v>-11529</v>
+        <v>7</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="K44" s="2" cm="1">
         <f t="array" ref="K44">+_xlfn.IFNA(SUM(G44:J44),blank)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16">
-      <c r="B45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D45" s="8">
-        <v>-6946</v>
-      </c>
+    <row r="45" spans="1:26" s="11" customFormat="1" ht="15">
+      <c r="A45" s="35"/>
+      <c r="B45" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
       <c r="K45" s="2" cm="1">
         <f t="array" ref="K45">+_xlfn.IFNA(SUM(G45:J45),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:16">
-      <c r="B46" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D46" s="8">
-        <v>207</v>
-      </c>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
+    </row>
+    <row r="46" spans="1:26" s="12" customFormat="1" ht="15">
+      <c r="A46" s="36"/>
+      <c r="B46" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
       <c r="K46" s="2" cm="1">
         <f t="array" ref="K46">+_xlfn.IFNA(SUM(G46:J46),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" s="5" customFormat="1">
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
+    </row>
+    <row r="47" spans="1:26" s="5" customFormat="1">
       <c r="A47" s="33"/>
-      <c r="B47" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="8">
-        <v>1144</v>
-      </c>
-      <c r="K47" s="5" cm="1">
+      <c r="B47" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2" cm="1">
         <f t="array" ref="K47">+_xlfn.IFNA(SUM(G47:J47),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" s="11" customFormat="1" ht="15">
-      <c r="A48" s="35"/>
-      <c r="B48" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="10">
-        <v>130</v>
-      </c>
-      <c r="K48" s="11" cm="1">
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+    </row>
+    <row r="48" spans="1:26">
+      <c r="E48" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K48" s="2" cm="1">
         <f t="array" ref="K48">+_xlfn.IFNA(SUM(G48:J48),blank)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="2:11">
-      <c r="B49" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C49" s="5"/>
-      <c r="D49" s="9">
-        <f>+D43+D44+D45+D46+D47-D48</f>
-        <v>-123714</v>
+      <c r="P48" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="49" spans="1:26">
+      <c r="B49" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D49" s="8">
+        <v>95736</v>
       </c>
       <c r="K49" s="2" cm="1">
         <f t="array" ref="K49">+_xlfn.IFNA(SUM(G49:J49),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26">
+      <c r="B50" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="14">
+        <v>102393</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
+      <c r="H50" s="13"/>
+      <c r="I50" s="13"/>
+      <c r="J50" s="13"/>
+      <c r="K50" s="13" cm="1">
+        <f t="array" ref="K50">+_xlfn.IFNA(SUM(G50:J50),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L50" s="13"/>
+      <c r="M50" s="13"/>
+      <c r="N50" s="13"/>
+      <c r="O50" s="13"/>
+      <c r="P50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q50" s="13"/>
+      <c r="R50" s="13"/>
+      <c r="S50" s="13"/>
+      <c r="T50" s="13"/>
+      <c r="U50" s="13"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="13"/>
+      <c r="Z50" s="13"/>
+    </row>
+    <row r="51" spans="1:26" s="5" customFormat="1">
+      <c r="A51" s="33"/>
+      <c r="B51" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D51" s="9">
+        <f>+D49-D50</f>
+        <v>-6657</v>
+      </c>
+      <c r="K51" s="5" cm="1">
+        <f t="array" ref="K51">+_xlfn.IFNA(SUM(G51:J51),blank)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:26" s="11" customFormat="1" ht="15">
+      <c r="A52" s="35"/>
+      <c r="B52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="2"/>
+      <c r="D52" s="8">
+        <v>37871</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2" cm="1">
+        <f t="array" ref="K52">+_xlfn.IFNA(SUM(G52:J52),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="2"/>
+      <c r="R52" s="2"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="2"/>
+      <c r="U52" s="2"/>
+      <c r="V52" s="2"/>
+      <c r="W52" s="2"/>
+      <c r="X52" s="2"/>
+      <c r="Y52" s="2"/>
+      <c r="Z52" s="2"/>
+    </row>
+    <row r="53" spans="1:26">
+      <c r="B53" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="8">
+        <v>34913</v>
+      </c>
+      <c r="K53" s="2" cm="1">
+        <f t="array" ref="K53">+_xlfn.IFNA(SUM(G53:J53),blank)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" ht="15">
+      <c r="B54" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D54" s="10">
+        <v>27019</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="5" cm="1">
+        <f t="array" ref="K54">+_xlfn.IFNA(SUM(G54:J54),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+      <c r="R54" s="11"/>
+      <c r="S54" s="11"/>
+      <c r="T54" s="11"/>
+      <c r="U54" s="11"/>
+      <c r="V54" s="11"/>
+      <c r="W54" s="11"/>
+      <c r="X54" s="11"/>
+      <c r="Y54" s="11"/>
+      <c r="Z54" s="11"/>
+    </row>
+    <row r="55" spans="1:26" ht="15">
+      <c r="B55" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" s="10">
+        <f>+SUM(D52:D54)</f>
+        <v>99803</v>
+      </c>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="12"/>
+      <c r="H55" s="12"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12" cm="1">
+        <f t="array" ref="K55">+_xlfn.IFNA(SUM(G55:J55),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="12"/>
+      <c r="P55" s="12"/>
+      <c r="Q55" s="12"/>
+      <c r="R55" s="12"/>
+      <c r="S55" s="12"/>
+      <c r="T55" s="12"/>
+      <c r="U55" s="12"/>
+      <c r="V55" s="12"/>
+      <c r="W55" s="12"/>
+      <c r="X55" s="12"/>
+      <c r="Y55" s="12"/>
+      <c r="Z55" s="12"/>
+    </row>
+    <row r="56" spans="1:26">
+      <c r="B56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C56" s="5"/>
+      <c r="D56" s="9">
+        <f>+D51-D55</f>
+        <v>-106460</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5"/>
+      <c r="K56" s="5" cm="1">
+        <f t="array" ref="K56">+_xlfn.IFNA(SUM(G56:J56),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L56" s="5"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="5"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="5"/>
+      <c r="R56" s="5"/>
+      <c r="S56" s="5"/>
+      <c r="T56" s="5"/>
+      <c r="U56" s="5"/>
+      <c r="V56" s="5"/>
+      <c r="W56" s="5"/>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
+      <c r="Z56" s="5"/>
+    </row>
+    <row r="57" spans="1:26">
+      <c r="B57" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D57" s="8">
+        <v>-11529</v>
+      </c>
+      <c r="K57" s="2" cm="1">
+        <f t="array" ref="K57">+_xlfn.IFNA(SUM(G57:J57),blank)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:26">
+      <c r="B58" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D58" s="8">
+        <v>-6946</v>
+      </c>
+      <c r="K58" s="2" cm="1">
+        <f t="array" ref="K58">+_xlfn.IFNA(SUM(G58:J58),blank)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26">
+      <c r="B59" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D59" s="8">
+        <v>207</v>
+      </c>
+      <c r="K59" s="2" cm="1">
+        <f t="array" ref="K59">+_xlfn.IFNA(SUM(G59:J59),blank)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26">
+      <c r="B60" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60" s="8">
+        <v>1144</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5"/>
+      <c r="K60" s="5" cm="1">
+        <f t="array" ref="K60">+_xlfn.IFNA(SUM(G60:J60),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L60" s="5"/>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5"/>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5"/>
+      <c r="U60" s="5"/>
+      <c r="V60" s="5"/>
+      <c r="W60" s="5"/>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="5"/>
+    </row>
+    <row r="61" spans="1:26" ht="15">
+      <c r="B61" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="10">
+        <v>130</v>
+      </c>
+      <c r="E61" s="11"/>
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+      <c r="H61" s="11"/>
+      <c r="I61" s="11"/>
+      <c r="J61" s="11"/>
+      <c r="K61" s="11" cm="1">
+        <f t="array" ref="K61">+_xlfn.IFNA(SUM(G61:J61),blank)</f>
+        <v>0</v>
+      </c>
+      <c r="L61" s="11"/>
+      <c r="M61" s="11"/>
+      <c r="N61" s="11"/>
+      <c r="O61" s="11"/>
+      <c r="P61" s="11"/>
+      <c r="Q61" s="11"/>
+      <c r="R61" s="11"/>
+      <c r="S61" s="11"/>
+      <c r="T61" s="11"/>
+      <c r="U61" s="11"/>
+      <c r="V61" s="11"/>
+      <c r="W61" s="11"/>
+      <c r="X61" s="11"/>
+      <c r="Y61" s="11"/>
+      <c r="Z61" s="11"/>
+    </row>
+    <row r="62" spans="1:26">
+      <c r="B62" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="9">
+        <f>+D56+D57+D58+D59+D60-D61</f>
+        <v>-123714</v>
+      </c>
+      <c r="K62" s="2" cm="1">
+        <f t="array" ref="K62">+_xlfn.IFNA(SUM(G62:J62),blank)</f>
         <v>0</v>
       </c>
     </row>
@@ -1773,4 +2403,805 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{320604BF-54C5-4CE9-AAD5-BF9F03B314AD}">
+  <dimension ref="A1:Z26"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
+    <col min="2" max="6" width="9.140625" style="1"/>
+    <col min="7" max="11" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" s="40"/>
+    </row>
+    <row r="2" spans="1:26" ht="15">
+      <c r="C2" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="P2" s="55"/>
+      <c r="Q2" s="55"/>
+      <c r="R2" s="55"/>
+      <c r="S2" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="T2" s="55"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="55"/>
+      <c r="W2" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="X2" s="55"/>
+      <c r="Y2" s="55"/>
+      <c r="Z2" s="55"/>
+    </row>
+    <row r="3" spans="1:26" ht="15">
+      <c r="C3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="P3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="R3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="T3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="X3" s="54" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y3" s="54" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z3" s="54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26">
+      <c r="B8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="56"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
+      <c r="F8" s="56"/>
+      <c r="G8" s="56">
+        <v>-29293</v>
+      </c>
+      <c r="H8" s="56">
+        <v>-38668</v>
+      </c>
+      <c r="I8" s="56">
+        <v>-20081</v>
+      </c>
+      <c r="J8" s="56">
+        <v>-35154</v>
+      </c>
+      <c r="K8" s="56">
+        <v>-12628</v>
+      </c>
+      <c r="L8" s="56">
+        <v>-22592</v>
+      </c>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="56"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="56"/>
+    </row>
+    <row r="9" spans="1:26">
+      <c r="B9" s="57" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" s="56"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56">
+        <f>+H9</f>
+        <v>13124</v>
+      </c>
+      <c r="H9" s="56">
+        <v>13124</v>
+      </c>
+      <c r="I9" s="58">
+        <f>36365-SUM(G9:H9)</f>
+        <v>10117</v>
+      </c>
+      <c r="J9" s="56">
+        <f>45637-SUM(G9:I9)</f>
+        <v>9272</v>
+      </c>
+      <c r="K9" s="56">
+        <f>+L9</f>
+        <v>10852</v>
+      </c>
+      <c r="L9" s="56">
+        <v>10852</v>
+      </c>
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="56"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+    </row>
+    <row r="10" spans="1:26">
+      <c r="B10" s="57" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="56"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
+      <c r="K10" s="56"/>
+      <c r="L10" s="56"/>
+      <c r="M10" s="56"/>
+      <c r="N10" s="56"/>
+      <c r="O10" s="56"/>
+      <c r="P10" s="56"/>
+      <c r="Q10" s="56"/>
+      <c r="R10" s="56"/>
+      <c r="S10" s="56"/>
+      <c r="T10" s="56"/>
+      <c r="U10" s="56"/>
+      <c r="V10" s="56"/>
+      <c r="W10" s="56"/>
+      <c r="X10" s="56"/>
+      <c r="Y10" s="56"/>
+      <c r="Z10" s="56"/>
+    </row>
+    <row r="11" spans="1:26">
+      <c r="B11" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="56"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="56"/>
+      <c r="G11" s="56"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="56"/>
+      <c r="K11" s="56"/>
+      <c r="L11" s="56"/>
+      <c r="M11" s="56"/>
+      <c r="N11" s="56"/>
+      <c r="O11" s="56"/>
+      <c r="P11" s="56"/>
+      <c r="Q11" s="56"/>
+      <c r="R11" s="56"/>
+      <c r="S11" s="56"/>
+      <c r="T11" s="56"/>
+      <c r="U11" s="56"/>
+      <c r="V11" s="56"/>
+      <c r="W11" s="56"/>
+      <c r="X11" s="56"/>
+      <c r="Y11" s="56"/>
+      <c r="Z11" s="56"/>
+    </row>
+    <row r="12" spans="1:26">
+      <c r="C12" s="56"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56">
+        <f>+G8+G9+G10-G11</f>
+        <v>-16169</v>
+      </c>
+      <c r="H12" s="56">
+        <f t="shared" ref="H12:L12" si="0">+H8+H9+H10-H11</f>
+        <v>-25544</v>
+      </c>
+      <c r="I12" s="56">
+        <f t="shared" si="0"/>
+        <v>-9964</v>
+      </c>
+      <c r="J12" s="56">
+        <f t="shared" si="0"/>
+        <v>-25882</v>
+      </c>
+      <c r="K12" s="56">
+        <f t="shared" si="0"/>
+        <v>-1776</v>
+      </c>
+      <c r="L12" s="56">
+        <f t="shared" si="0"/>
+        <v>-11740</v>
+      </c>
+      <c r="M12" s="56"/>
+      <c r="N12" s="56"/>
+      <c r="O12" s="56"/>
+      <c r="P12" s="56"/>
+      <c r="Q12" s="56"/>
+      <c r="R12" s="56"/>
+      <c r="S12" s="56"/>
+      <c r="T12" s="56"/>
+      <c r="U12" s="56"/>
+      <c r="V12" s="56"/>
+      <c r="W12" s="56"/>
+      <c r="X12" s="56"/>
+      <c r="Y12" s="56"/>
+      <c r="Z12" s="56"/>
+    </row>
+    <row r="13" spans="1:26">
+      <c r="C13" s="56"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
+      <c r="F13" s="56"/>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+      <c r="J13" s="56"/>
+      <c r="K13" s="56"/>
+      <c r="L13" s="56"/>
+      <c r="M13" s="56"/>
+      <c r="N13" s="56"/>
+      <c r="O13" s="56"/>
+      <c r="P13" s="56"/>
+      <c r="Q13" s="56"/>
+      <c r="R13" s="56"/>
+      <c r="S13" s="56"/>
+      <c r="T13" s="56"/>
+      <c r="U13" s="56"/>
+      <c r="V13" s="56"/>
+      <c r="W13" s="56"/>
+      <c r="X13" s="56"/>
+      <c r="Y13" s="56"/>
+      <c r="Z13" s="56"/>
+    </row>
+    <row r="14" spans="1:26">
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+      <c r="J14" s="56"/>
+      <c r="K14" s="56"/>
+      <c r="L14" s="56"/>
+      <c r="M14" s="56"/>
+      <c r="N14" s="56"/>
+      <c r="O14" s="56"/>
+      <c r="P14" s="56"/>
+      <c r="Q14" s="56"/>
+      <c r="R14" s="56"/>
+      <c r="S14" s="56"/>
+      <c r="T14" s="56"/>
+      <c r="U14" s="56"/>
+      <c r="V14" s="56"/>
+      <c r="W14" s="56"/>
+      <c r="X14" s="56"/>
+      <c r="Y14" s="56"/>
+      <c r="Z14" s="56"/>
+    </row>
+    <row r="15" spans="1:26">
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+      <c r="J15" s="56"/>
+      <c r="K15" s="56">
+        <f>+SUM(H12:K12)</f>
+        <v>-63166</v>
+      </c>
+      <c r="L15" s="56">
+        <v>1000000</v>
+      </c>
+      <c r="M15" s="56"/>
+      <c r="N15" s="56"/>
+      <c r="O15" s="56"/>
+      <c r="P15" s="56"/>
+      <c r="Q15" s="56"/>
+      <c r="R15" s="56"/>
+      <c r="S15" s="56"/>
+      <c r="T15" s="56"/>
+      <c r="U15" s="56"/>
+      <c r="V15" s="56"/>
+      <c r="W15" s="56"/>
+      <c r="X15" s="56"/>
+      <c r="Y15" s="56"/>
+      <c r="Z15" s="56"/>
+    </row>
+    <row r="16" spans="1:26">
+      <c r="C16" s="56"/>
+      <c r="D16" s="56"/>
+      <c r="E16" s="56"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+      <c r="J16" s="56"/>
+      <c r="K16" s="56"/>
+      <c r="L16" s="59">
+        <f>+L15/K15-1</f>
+        <v>-16.831301649621633</v>
+      </c>
+      <c r="M16" s="56"/>
+      <c r="N16" s="56"/>
+      <c r="O16" s="56"/>
+      <c r="P16" s="56"/>
+      <c r="Q16" s="56"/>
+      <c r="R16" s="56"/>
+      <c r="S16" s="56"/>
+      <c r="T16" s="56"/>
+      <c r="U16" s="56"/>
+      <c r="V16" s="56"/>
+      <c r="W16" s="56"/>
+      <c r="X16" s="56"/>
+      <c r="Y16" s="56"/>
+      <c r="Z16" s="56"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="B18" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="L18" s="56">
+        <v>4900000</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="B19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="56">
+        <v>261000</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="B20" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L20" s="56">
+        <v>182000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="B21" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="L21" s="58">
+        <f>+L18+L19-L20</f>
+        <v>4979000</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="L24" s="60">
+        <f>+L15/L21</f>
+        <v>0.2008435428800964</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="L25" s="60">
+        <v>1.66E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="L26" s="1">
+        <f>+L24/L25</f>
+        <v>12.099008607234722</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="O2:R2"/>
+    <mergeCell ref="S2:V2"/>
+    <mergeCell ref="W2:Z2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD08170A-1BF4-498F-84A6-20219A0DC4ED}">
+  <dimension ref="B2:R19"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="9" width="10.7109375" style="1" customWidth="1"/>
+    <col min="10" max="12" width="20.7109375" style="1" customWidth="1"/>
+    <col min="13" max="18" width="17.7109375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:18">
+      <c r="B2" s="41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="2:18" ht="15">
+      <c r="C4" s="43" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="44" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44" t="s">
+        <v>100</v>
+      </c>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="44"/>
+    </row>
+    <row r="5" spans="2:18" ht="14.25">
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="F5" s="43" t="s">
+        <v>91</v>
+      </c>
+      <c r="G5" s="43" t="s">
+        <v>93</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>95</v>
+      </c>
+      <c r="J5" s="43" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="42"/>
+      <c r="M5" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="N5" s="42"/>
+      <c r="O5" s="42"/>
+      <c r="P5" s="43" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="43" t="s">
+        <v>103</v>
+      </c>
+      <c r="R5" s="43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18">
+      <c r="B6" s="41" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18">
+      <c r="B7" s="45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="46"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="46"/>
+      <c r="L7" s="46"/>
+      <c r="M7" s="46"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="46"/>
+      <c r="P7" s="46"/>
+      <c r="Q7" s="46"/>
+      <c r="R7" s="47"/>
+    </row>
+    <row r="8" spans="2:18">
+      <c r="B8" s="48" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="49"/>
+      <c r="Q8" s="49"/>
+      <c r="R8" s="50"/>
+    </row>
+    <row r="9" spans="2:18">
+      <c r="B9" s="48" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="49"/>
+      <c r="O9" s="49"/>
+      <c r="P9" s="49"/>
+      <c r="Q9" s="49"/>
+      <c r="R9" s="50"/>
+    </row>
+    <row r="10" spans="2:18">
+      <c r="B10" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
+      <c r="K10" s="49"/>
+      <c r="L10" s="49"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="49"/>
+      <c r="O10" s="49"/>
+      <c r="P10" s="49"/>
+      <c r="Q10" s="49"/>
+      <c r="R10" s="50"/>
+    </row>
+    <row r="11" spans="2:18">
+      <c r="B11" s="51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="53"/>
+    </row>
+    <row r="13" spans="2:18">
+      <c r="B13" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18">
+      <c r="B14" s="45" t="s">
+        <v>81</v>
+      </c>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="46"/>
+      <c r="L14" s="46"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="46"/>
+      <c r="O14" s="46"/>
+      <c r="P14" s="46"/>
+      <c r="Q14" s="46"/>
+      <c r="R14" s="47"/>
+    </row>
+    <row r="15" spans="2:18">
+      <c r="B15" s="48" t="s">
+        <v>82</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="49"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="49"/>
+      <c r="J15" s="49"/>
+      <c r="K15" s="49"/>
+      <c r="L15" s="49"/>
+      <c r="M15" s="49"/>
+      <c r="N15" s="49"/>
+      <c r="O15" s="49"/>
+      <c r="P15" s="49"/>
+      <c r="Q15" s="49"/>
+      <c r="R15" s="50"/>
+    </row>
+    <row r="16" spans="2:18">
+      <c r="B16" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+      <c r="M16" s="49"/>
+      <c r="N16" s="49"/>
+      <c r="O16" s="49"/>
+      <c r="P16" s="49"/>
+      <c r="Q16" s="49"/>
+      <c r="R16" s="50"/>
+    </row>
+    <row r="17" spans="2:18">
+      <c r="B17" s="51" t="s">
+        <v>86</v>
+      </c>
+      <c r="C17" s="52"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="52"/>
+      <c r="H17" s="52"/>
+      <c r="I17" s="52"/>
+      <c r="J17" s="52"/>
+      <c r="K17" s="52"/>
+      <c r="L17" s="52"/>
+      <c r="M17" s="52"/>
+      <c r="N17" s="52"/>
+      <c r="O17" s="52"/>
+      <c r="P17" s="52"/>
+      <c r="Q17" s="52"/>
+      <c r="R17" s="53"/>
+    </row>
+    <row r="19" spans="2:18" ht="14.25">
+      <c r="B19" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="M4:O4"/>
+    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>